--- a/salon_forms/040_skin_client_record_form--salon_forms.xlsx
+++ b/salon_forms/040_skin_client_record_form--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'service_provider_1'}</t>
+          <t>service_provider_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Service Provider 1'}</t>
+          <t>Service Provider 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'service_provider_2'}</t>
+          <t>service_provider_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Service Provider 2'}</t>
+          <t>Service Provider 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'service_provider_3'}</t>
+          <t>service_provider_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Service Provider 3'}</t>
+          <t>Service Provider 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'acne'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Acne'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'aging'}</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Aging'}</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'blackheads'}</t>
+          <t>blackheads</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Blackheads'}</t>
+          <t>Blackheads</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'bumps'}</t>
+          <t>bumps</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Bumps'}</t>
+          <t>Bumps</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'burns'}</t>
+          <t>burns</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Burns'}</t>
+          <t>Burns</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'cold_sores'}</t>
+          <t>cold_sores</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Cold Sores'}</t>
+          <t>Cold Sores</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'eczema'}</t>
+          <t>eczema</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Eczema'}</t>
+          <t>Eczema</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'keloids'}</t>
+          <t>keloids</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Keloids'}</t>
+          <t>Keloids</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'moles'}</t>
+          <t>moles</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Moles'}</t>
+          <t>Moles</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'pigmentation'}</t>
+          <t>pigmentation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Pigmentation'}</t>
+          <t>Pigmentation</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'psoriasis'}</t>
+          <t>psoriasis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Psoriasis'}</t>
+          <t>Psoriasis</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'rosacea'}</t>
+          <t>rosacea</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Rosacea'}</t>
+          <t>Rosacea</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'skin_tag'}</t>
+          <t>skin_tag</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Skin Tag'}</t>
+          <t>Skin Tag</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'warts'}</t>
+          <t>warts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Warts'}</t>
+          <t>Warts</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'service_1'}</t>
+          <t>service_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Service 1'}</t>
+          <t>Service 1</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'service_2'}</t>
+          <t>service_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Service 2'}</t>
+          <t>Service 2</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'service_3'}</t>
+          <t>service_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Service 3'}</t>
+          <t>Service 3</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'provider_1'}</t>
+          <t>provider_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Provider 1'}</t>
+          <t>Provider 1</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'provider_2'}</t>
+          <t>provider_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Provider 2'}</t>
+          <t>Provider 2</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'provider_3'}</t>
+          <t>provider_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Provider 3'}</t>
+          <t>Provider 3</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'appointment_1'}</t>
+          <t>appointment_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Appointment 1'}</t>
+          <t>Appointment 1</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'appointment_2'}</t>
+          <t>appointment_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Appointment 2'}</t>
+          <t>Appointment 2</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'appointment_3'}</t>
+          <t>appointment_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Appointment 3'}</t>
+          <t>Appointment 3</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'review_1'}</t>
+          <t>review_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Review 1'}</t>
+          <t>Review 1</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'review_2'}</t>
+          <t>review_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Review 2'}</t>
+          <t>Review 2</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'review_3'}</t>
+          <t>review_3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Review 3'}</t>
+          <t>Review 3</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'article_1'}</t>
+          <t>article_1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Article 1'}</t>
+          <t>Article 1</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'article_2'}</t>
+          <t>article_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Article 2'}</t>
+          <t>Article 2</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'article_3'}</t>
+          <t>article_3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Article 3'}</t>
+          <t>Article 3</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'video_1'}</t>
+          <t>video_1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Video 1'}</t>
+          <t>Video 1</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'video_2'}</t>
+          <t>video_2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Video 2'}</t>
+          <t>Video 2</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'video_3'}</t>
+          <t>video_3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Video 3'}</t>
+          <t>Video 3</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'website_1'}</t>
+          <t>website_1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Website 1'}</t>
+          <t>Website 1</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'website_2'}</t>
+          <t>website_2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Website 2'}</t>
+          <t>Website 2</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'website_3'}</t>
+          <t>website_3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Website 3'}</t>
+          <t>Website 3</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'book_1'}</t>
+          <t>book_1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Book 1'}</t>
+          <t>Book 1</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'book_2'}</t>
+          <t>book_2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Book 2'}</t>
+          <t>Book 2</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'book_3'}</t>
+          <t>book_3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Book 3'}</t>
+          <t>Book 3</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'blog_1'}</t>
+          <t>blog_1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Blog 1'}</t>
+          <t>Blog 1</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'blog_2'}</t>
+          <t>blog_2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Blog 2'}</t>
+          <t>Blog 2</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'blog_3'}</t>
+          <t>blog_3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Blog 3'}</t>
+          <t>Blog 3</t>
         </is>
       </c>
     </row>
